--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; -2,17</t>
+          <t>-11,29; -2,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,84</t>
+          <t>-5,52; 4,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,84</t>
+          <t>-7,08; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,4</t>
+          <t>3,56; 11,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -1,1</t>
+          <t>-7,89; -1,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,56</t>
+          <t>1,15; 7,4</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,61; -6,57</t>
+          <t>-28,92; -5,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 13,64</t>
+          <t>-14,53; 13,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 3,78</t>
+          <t>-13,29; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 23,07</t>
+          <t>6,65; 22,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,32; -2,37</t>
+          <t>-16,82; -3,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 17,25</t>
+          <t>2,55; 17,01</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,28</t>
+          <t>-0,67; 3,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,97</t>
+          <t>-0,25; 7,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,99</t>
+          <t>-1,19; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 9,24</t>
+          <t>-0,68; 9,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,09</t>
+          <t>-0,14; 3,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,65</t>
+          <t>1,2; 7,72</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 38,21</t>
+          <t>-6,45; 36,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 77,84</t>
+          <t>-1,26; 77,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 25,14</t>
+          <t>-6,13; 27,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 56,34</t>
+          <t>-3,59; 55,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 25,02</t>
+          <t>-1,02; 25,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 59,69</t>
+          <t>8,95; 60,36</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,17</t>
+          <t>-0,85; 6,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,73</t>
+          <t>2,8; 9,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,64</t>
+          <t>-4,55; 3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 15,57</t>
+          <t>7,35; 16,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,96</t>
+          <t>-1,63; 3,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,79</t>
+          <t>6,03; 11,74</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 122,86</t>
+          <t>-14,55; 138,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,4; 203,71</t>
+          <t>32,06; 219,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 44,52</t>
+          <t>-35,59; 45,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,43; 188,75</t>
+          <t>54,23; 201,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 54,4</t>
+          <t>-17,06; 51,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,69; 172,3</t>
+          <t>58,46; 168,94</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,22</t>
+          <t>-3,98; -0,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,46</t>
+          <t>-3,56; 2,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -1,12</t>
+          <t>-5,4; -0,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,72</t>
+          <t>-4,37; 3,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -1,15</t>
+          <t>-4,09; -1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,59</t>
+          <t>-2,77; 2,72</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -1,38</t>
+          <t>-22,09; -1,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 14,92</t>
+          <t>-20,93; 14,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,05; -3,89</t>
+          <t>-18,05; -3,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 13,06</t>
+          <t>-14,67; 14,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -5,1</t>
+          <t>-17,04; -5,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 11,22</t>
+          <t>-11,9; 12,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -2,12</t>
+          <t>-11,4; -2,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 4,81</t>
+          <t>-7,23; 2,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1,87</t>
+          <t>-7,04; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,09</t>
+          <t>2,63; 10,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,45</t>
+          <t>-7,66; -0,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 7,4</t>
+          <t>-0,04; 6,27</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0,87%</t>
+          <t>-5,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,92; -5,84</t>
+          <t>-29,05; -7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 13,97</t>
+          <t>-18,63; 7,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 3,74</t>
+          <t>-13,32; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 22,49</t>
+          <t>4,88; 20,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -3,25</t>
+          <t>-16,5; -2,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 17,01</t>
+          <t>-0,08; 14,39</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>7,57</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,2</t>
+          <t>-0,79; 3,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,08</t>
+          <t>3,89; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,24</t>
+          <t>-0,95; 4,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 9,25</t>
+          <t>6,66; 11,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,12</t>
+          <t>-0,25; 3,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,72</t>
+          <t>6,0; 9,22</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 36,0</t>
+          <t>-7,02; 37,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 77,85</t>
+          <t>35,62; 93,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 27,09</t>
+          <t>-5,3; 28,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 55,82</t>
+          <t>35,61; 74,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 25,2</t>
+          <t>-1,73; 24,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 60,36</t>
+          <t>42,68; 75,43</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,02</t>
+          <t>9,27</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,33</t>
+          <t>-0,9; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,79</t>
+          <t>2,51; 9,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,74</t>
+          <t>-4,63; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 16,03</t>
+          <t>7,89; 16,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,86</t>
+          <t>-1,35; 4,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,74</t>
+          <t>6,4; 12,05</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108,93%</t>
+          <t>112,39%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>105,92%</t>
+          <t>108,85%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 138,59</t>
+          <t>-12,54; 123,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,06; 219,46</t>
+          <t>29,87; 213,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 45,22</t>
+          <t>-36,0; 37,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,23; 201,36</t>
+          <t>55,55; 193,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 51,78</t>
+          <t>-14,36; 54,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,46; 168,94</t>
+          <t>59,46; 167,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>2,28</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,32</t>
+          <t>-3,95; -0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,44</t>
+          <t>-0,87; 2,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -0,94</t>
+          <t>-5,33; -1,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,99</t>
+          <t>1,1; 5,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -1,14</t>
+          <t>-4,13; -1,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,72</t>
+          <t>0,94; 3,69</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,09; -1,59</t>
+          <t>-22,08; -1,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 14,97</t>
+          <t>-4,95; 17,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,05; -3,41</t>
+          <t>-17,67; -3,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 14,22</t>
+          <t>3,53; 19,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,04; -5,14</t>
+          <t>-17,09; -5,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 12,07</t>
+          <t>4,06; 16,53</t>
         </is>
       </c>
     </row>
